--- a/artfynd/A 40045-2025 artfynd.xlsx
+++ b/artfynd/A 40045-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104090700</v>
+        <v>76511349</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Märkeshult mot SSV, Hl</t>
+          <t>Bårarp, träd N10327, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368029.9315951617</v>
+        <v>367946</v>
       </c>
       <c r="R2" t="n">
-        <v>6300861.446576385</v>
+        <v>6300900</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +735,32 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Slättåkra</t>
+          <t>Getinge</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>N10327</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2014-08-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2014-08-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,27 +769,156 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsväg i granåker fuktdrag</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jennie Thronée</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104090700</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Märkeshult mot SSV, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>368030</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6300861</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Slättåkra</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skogsväg i granåker fuktdrag</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40045-2025 artfynd.xlsx
+++ b/artfynd/A 40045-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76511349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,8 +929,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104090700</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>